--- a/mapping-version2/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/mapping-version2/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:40:45+00:00</t>
+    <t>2026-06-16T12:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-version2/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/mapping-version2/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:42:54+00:00</t>
+    <t>2026-06-16T12:43:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
